--- a/Datasets/14 Species for Taxon ID and jurisdiction species ID.xlsx
+++ b/Datasets/14 Species for Taxon ID and jurisdiction species ID.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmollick\Documents\iMapML\Datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C076F9FD-AE36-4E21-A38A-E4A5229C78DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71FBC7D-4590-459E-9744-16D87E0B4F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{EDD41942-0EA8-40FD-9CC5-2AD9CA86FB2B}"/>
   </bookViews>

--- a/Datasets/14 Species for Taxon ID and jurisdiction species ID.xlsx
+++ b/Datasets/14 Species for Taxon ID and jurisdiction species ID.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmollick\Documents\iMapML\Datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71FBC7D-4590-459E-9744-16D87E0B4F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C6D6D2-9357-4B6C-A8DC-1CC31C215158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{EDD41942-0EA8-40FD-9CC5-2AD9CA86FB2B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EDD41942-0EA8-40FD-9CC5-2AD9CA86FB2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
   <si>
     <t>Common name</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>Phragmites</t>
+  </si>
+  <si>
+    <t>Modified_threshold</t>
   </si>
 </sst>
 </file>
@@ -575,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E54C7EA-30F2-4E7C-B9C7-7E778CC520A0}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.28515625" bestFit="1" customWidth="1"/>
@@ -586,7 +589,7 @@
     <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -605,8 +608,11 @@
       <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -626,7 +632,7 @@
         <v>30.56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -646,7 +652,7 @@
         <v>30.56</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -666,7 +672,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -686,7 +692,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -706,7 +712,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -726,7 +732,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -746,7 +752,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -766,7 +772,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -783,7 +789,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -803,7 +809,7 @@
         <v>23.79</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -823,7 +829,7 @@
         <v>21.54</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -843,7 +849,7 @@
         <v>31.47</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -863,7 +869,7 @@
         <v>39.89</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -883,7 +889,7 @@
         <v>21.26</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
